--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.asc.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.asc.xlsx
@@ -670,10 +670,33 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
+      <c r="B7" s="6" t="n">
+        <v>1004</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>训练假人</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>引导阶段的假人</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="6" t="n"/>

--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.asc.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.asc.xlsx
@@ -6,50 +6,141 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+  <si>
+    <t>##var</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Desc</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Tag</t>
+  </si>
+  <si>
+    <t>AttrSet</t>
+  </si>
+  <si>
+    <t>Ability</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>(array#sep=;),int</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>名字</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>等级</t>
+  </si>
+  <si>
+    <t>初始标签</t>
+  </si>
+  <si>
+    <t>初始属性集</t>
+  </si>
+  <si>
+    <t>初始技能</t>
+  </si>
+  <si>
+    <t>玩家</t>
+  </si>
+  <si>
+    <t>描述1</t>
+  </si>
+  <si>
+    <t>1001;400;2001</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>10001;10002;20001;5000</t>
+  </si>
+  <si>
+    <t>野怪1</t>
+  </si>
+  <si>
+    <t>描述2</t>
+  </si>
+  <si>
+    <t>boss1</t>
+  </si>
+  <si>
+    <t>描述3</t>
+  </si>
+  <si>
+    <t>1001;2002;2005;2006</t>
+  </si>
+  <si>
+    <t>10002</t>
+  </si>
+  <si>
+    <t>训练假人</t>
+  </si>
+  <si>
+    <t>引导阶段的假人</t>
+  </si>
+  <si>
+    <t>1002</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <family val="3"/>
-      <b val="1"/>
-      <color indexed="81"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <family val="3"/>
-      <color indexed="81"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -66,22 +157,18 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+  <cellXfs count="5">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,354 +534,270 @@
   <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
-    <col width="16.21875" customWidth="1" style="4" min="3" max="3"/>
-    <col width="14.44140625" customWidth="1" style="4" min="4" max="5"/>
-    <col width="15.88671875" customWidth="1" style="4" min="6" max="6"/>
-    <col width="20.21875" customWidth="1" style="4" min="7" max="7"/>
-    <col width="20.6640625" customWidth="1" style="4" min="8" max="8"/>
+    <col min="3" max="3" width="16.21875" customWidth="1" style="3"/>
+    <col min="4" max="5" width="14.44140625" customWidth="1" style="3"/>
+    <col min="6" max="6" width="15.88671875" customWidth="1" style="3"/>
+    <col min="7" max="7" width="20.21875" customWidth="1" style="3"/>
+    <col min="8" max="8" width="20.6640625" customWidth="1" style="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C1" s="6" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D1" s="6" t="inlineStr">
-        <is>
-          <t>Desc</t>
-        </is>
-      </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>Level</t>
-        </is>
-      </c>
-      <c r="F1" s="6" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-      <c r="G1" s="6" t="inlineStr">
-        <is>
-          <t>AttrSet</t>
-        </is>
-      </c>
-      <c r="H1" s="6" t="inlineStr">
-        <is>
-          <t>Ability</t>
-        </is>
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>(array#sep=;),int</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>(array#sep=;),int</t>
-        </is>
-      </c>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>(array#sep=;),int</t>
-        </is>
+      <c r="A2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>##</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>名字</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>描述</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>等级</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>初始标签</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>初始属性集</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>初始技能</t>
-        </is>
+      <c r="A3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="n"/>
-      <c r="B4" s="6" t="n">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4">
         <v>1001</v>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>玩家</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>描述1</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="n">
+      <c r="C4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="4">
         <v>1</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>1001;400;2001</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>10001;10002;20001</t>
-        </is>
+      <c r="F4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="n"/>
-      <c r="B5" s="6" t="n">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4">
         <v>1002</v>
       </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>野怪1</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>描述2</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="n">
+      <c r="C5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="4">
         <v>0</v>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="B6" t="n">
+      <c r="B6" s="2">
         <v>1003</v>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>boss1</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>描述3</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="n">
+      <c r="C6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="4">
         <v>0</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1001;2002;2005;2006</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>10002</t>
-        </is>
+      <c r="F6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="4">
         <v>1004</v>
       </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>训练假人</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>引导阶段的假人</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="n">
+      <c r="C7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="4">
         <v>1</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1002</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="F7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="8">
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
     </row>
     <row r="9">
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
     </row>
     <row r="10">
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
     </row>
     <row r="11">
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
     </row>
     <row r="12">
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
     </row>
     <row r="13">
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
     </row>
     <row r="14">
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
     </row>
     <row r="15">
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
     </row>
     <row r="16">
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
     </row>
     <row r="17">
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
     </row>
     <row r="18">
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
     </row>
     <row r="19">
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
     </row>
     <row r="20">
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
     </row>
     <row r="21">
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
     </row>
     <row r="22">
-      <c r="B22" s="6" t="n"/>
+      <c r="B22" s="4"/>
     </row>
     <row r="23">
-      <c r="B23" s="6" t="n"/>
-    </row>
-    <row r="24"/>
+      <c r="B23" s="4"/>
+    </row>
     <row r="25">
-      <c r="B25" s="6" t="n"/>
+      <c r="B25" s="4"/>
     </row>
     <row r="26">
-      <c r="B26" s="6" t="n"/>
+      <c r="B26" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
+  <headerFooter/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>